--- a/data/TUG 5 agustus 2026.xlsx
+++ b/data/TUG 5 agustus 2026.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KERJAAN KANTOR\TUG\TUG Agustus 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\wms-pt.-bag\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45704D59-960D-401B-BBF1-25AB901F6C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7450592F-6616-4250-985C-1FBEC8FC65F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9B40D4F9-1AA9-44B2-B4D2-3A145A46AE6E}"/>
+    <workbookView minimized="1" xWindow="1480" yWindow="1480" windowWidth="19200" windowHeight="12080" xr2:uid="{9B40D4F9-1AA9-44B2-B4D2-3A145A46AE6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="118">
   <si>
     <t>No</t>
   </si>
@@ -370,6 +372,15 @@
   </si>
   <si>
     <t>Tanggal SPK</t>
+  </si>
+  <si>
+    <t>qwewqe</t>
+  </si>
+  <si>
+    <t>werwetwe</t>
+  </si>
+  <si>
+    <t>werwre</t>
   </si>
 </sst>
 </file>
@@ -1753,5 +1764,43 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDD541C-D1DB-4C61-AF63-5B1032D5044C}">
+  <dimension ref="C24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AA2FA4-B6EF-4CAB-85DE-D3BAC6BE6C97}">
+  <dimension ref="D12:D24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="12" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>